--- a/artfynd/A 61514-2025 artfynd.xlsx
+++ b/artfynd/A 61514-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>104220669</v>
+        <v>104220705</v>
       </c>
       <c r="B2" t="n">
-        <v>89412</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5442</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>682822.2957995529</v>
+        <v>682741</v>
       </c>
       <c r="R2" t="n">
-        <v>7101504.084769089</v>
+        <v>7101486</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +743,9 @@
           <t>2022-10-20</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2022-10-20</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -790,12 +775,7 @@
         <v>104230292</v>
       </c>
       <c r="B3" t="n">
-        <v>90657</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93201</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -827,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>682837.4267323493</v>
+        <v>682837</v>
       </c>
       <c r="R3" t="n">
-        <v>7101508.932217982</v>
+        <v>7101509</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -860,19 +840,9 @@
           <t>2022-10-20</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2022-10-20</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -900,6 +870,103 @@
           <t>Länsstyrelsens naturvärdesinventeringar i Västerbottens län</t>
         </is>
       </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>104220669</v>
+      </c>
+      <c r="B4" t="n">
+        <v>91930</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Gåsselåsen, Ång</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>682822</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7101504</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2022-10-20</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2022-10-20</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Isak Vahlström, Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
